--- a/outputs/tables/tabla_correlacion_rr_advi_nuts.xlsx
+++ b/outputs/tables/tabla_correlacion_rr_advi_nuts.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Modelo</t>
   </si>
@@ -34,16 +34,25 @@
     <t>N_Subcircuitos</t>
   </si>
   <si>
-    <t>Modelo (c) Besag ICAR + No Estructurado (Mejor LOO)</t>
+    <t>Modelo (b) Binomial Negativa (ICAR) [Mejor LOO]</t>
+  </si>
+  <si>
+    <t>Modelo (c) Besag ICAR + No Estructurado</t>
   </si>
   <si>
     <t>Modelo (d) BYM2 (Prior Beta(0.5, 0.5))</t>
   </si>
   <si>
+    <t>1.90e-283</t>
+  </si>
+  <si>
     <t>1.34e-246</t>
   </si>
   <si>
     <t>4.85e-243</t>
+  </si>
+  <si>
+    <t>6.65e-296</t>
   </si>
   <si>
     <t>3.07e-256</t>
@@ -407,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -435,16 +444,16 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.9952</v>
+        <v>0.9976</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>0.996</v>
+        <v>0.9981</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2">
         <v>244</v>
@@ -455,18 +464,38 @@
         <v>7</v>
       </c>
       <c r="B3">
+        <v>0.9952</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>0.996</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
         <v>0.9949</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
         <v>0.9959</v>
       </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3">
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4">
         <v>244</v>
       </c>
     </row>
